--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484687_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484687_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4961</v>
+        <v>5.1503</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1134</v>
+        <v>4.5942</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3826</v>
+        <v>0.556</v>
       </c>
       <c r="G2" t="n">
         <v>2.928</v>
@@ -610,13 +610,13 @@
         <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2041</v>
+        <v>-0.55</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8808</v>
+        <v>-0.4001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3233</v>
+        <v>-0.1499</v>
       </c>
       <c r="V2" t="n">
         <v>2.2224</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1044</v>
+        <v>1.8267</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0723</v>
+        <v>1.9184</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0322</v>
+        <v>-0.0917</v>
       </c>
       <c r="G3" t="n">
         <v>0.6191</v>
@@ -688,13 +688,13 @@
         <v>1.8326</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2183</v>
+        <v>-0.0594</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5362</v>
+        <v>0.3824</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3179</v>
+        <v>-0.4418</v>
       </c>
       <c r="V3" t="n">
         <v>1.267</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0305</v>
+        <v>-0.1355</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2083</v>
+        <v>-1.016</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1778</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-0.603</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0228</v>
+        <v>-0.0822</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3673</v>
+        <v>-0.175</v>
       </c>
       <c r="U5" t="n">
-        <v>0.39</v>
+        <v>0.0927</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0945</v>
+        <v>-0.3966</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1241</v>
+        <v>-1.4511</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0297</v>
+        <v>1.0545</v>
       </c>
       <c r="G6" t="n">
         <v>-1.0748</v>
@@ -922,13 +922,13 @@
         <v>2.1991</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.614</v>
+        <v>-0.9161</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9728</v>
+        <v>-0.2997</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6411</v>
+        <v>-0.6163</v>
       </c>
       <c r="V6" t="n">
         <v>0.3115</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.041</v>
+        <v>-1.8706</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9747</v>
+        <v>-0.8786</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0663</v>
+        <v>-0.992</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4963</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6284</v>
+        <v>-0.458</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4633</v>
+        <v>-0.389</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.9021</v>
+        <v>-2.6515</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.564</v>
+        <v>-2.6602</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3381</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-3.1223</v>
@@ -1078,13 +1078,13 @@
         <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.5633</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4744</v>
+        <v>0.3782</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2884</v>
+        <v>-0.9416</v>
       </c>
       <c r="V8" t="n">
         <v>0.3011</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.4461</v>
+        <v>-3.0397</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2405</v>
+        <v>-2.7597</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2057</v>
+        <v>-0.28</v>
       </c>
       <c r="G9" t="n">
         <v>-2.6824</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3972</v>
+        <v>0.0092</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1666</v>
+        <v>0.3141</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2306</v>
+        <v>-0.3049</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2097</v>
+        <v>-4.2127</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6766</v>
+        <v>-0.5805</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.5331</v>
+        <v>-3.6322</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9636</v>
@@ -1234,13 +1234,13 @@
         <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2199</v>
+        <v>-1.2229</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2398</v>
+        <v>-0.1436</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9801</v>
+        <v>-1.0792</v>
       </c>
       <c r="V10" t="n">
         <v>-0.0104</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>L. SALVADOR MONTANES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.5327</v>
+        <v>-4.4377</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0875</v>
+        <v>-3.1772</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4452</v>
+        <v>-1.2605</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.4717</v>
+        <v>-3.1187</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.3243</v>
+        <v>-4.0674</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8526</v>
+        <v>0.9487</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0595</v>
+        <v>-1.7097</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1428</v>
+        <v>-1.793</v>
       </c>
       <c r="L11" t="n">
         <v>0.0833</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4122</v>
+        <v>-1.4091</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1815</v>
+        <v>-2.2744</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7692</v>
+        <v>0.8653</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.733</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>0.829</v>
+        <v>-1.319</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4276</v>
+        <v>-0.5513</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5986</v>
+        <v>-0.7677</v>
       </c>
       <c r="V11" t="n">
-        <v>-3.157</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.5339</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L. SALVADOR MONTANES</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6242</v>
+        <v>-5.5131</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5619</v>
+        <v>-3.2413</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0623</v>
+        <v>-2.2718</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.1187</v>
+        <v>-1.4717</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.0674</v>
+        <v>-2.3243</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9487</v>
+        <v>0.8526</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7097</v>
+        <v>-1.0595</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.793</v>
+        <v>-1.1428</v>
       </c>
       <c r="L12" t="n">
         <v>0.0833</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4091</v>
+        <v>-0.4122</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.2744</v>
+        <v>-1.1815</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8653</v>
+        <v>0.7692</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.733</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5054</v>
+        <v>-0.1514</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9359</v>
+        <v>0.2738</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5696</v>
+        <v>-0.4252</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-3.157</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.3301</v>
+        <v>-14.3302</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.301699999999999</v>
+        <v>-8.3018</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.0284</v>
+        <v>-6.028499999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-9.035500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>12.8281</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.3129</v>
+        <v>-5.313099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2902</v>
+        <v>-0.2902000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.022900000000001</v>
+        <v>-5.0229</v>
       </c>
       <c r="V13" t="n">
         <v>0.9346000000000005</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>D. TOKAEV TOKAEV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5079</v>
+        <v>3.5251</v>
       </c>
       <c r="E14" t="n">
-        <v>5.1226</v>
+        <v>2.385</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3853</v>
+        <v>1.1401</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2769</v>
+        <v>4.057</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5527</v>
+        <v>3.5763</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2758</v>
+        <v>0.4807</v>
       </c>
       <c r="J14" t="n">
-        <v>3.778</v>
+        <v>3.8114</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6689</v>
+        <v>3.8114</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1091</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5011</v>
+        <v>0.2456</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1161</v>
+        <v>-0.2351</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3849</v>
+        <v>0.4807</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.733</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7489</v>
+        <v>-1.8326</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9091</v>
+        <v>0.5677</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7715</v>
+        <v>0.4061</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1375</v>
+        <v>0.1616</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.945</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. TOKAEV TOKAEV</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.7649</v>
+        <v>3.3896</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8273</v>
+        <v>3.1034</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9376</v>
+        <v>0.2862</v>
       </c>
       <c r="G15" t="n">
-        <v>4.057</v>
+        <v>3.2769</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5763</v>
+        <v>3.5527</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4807</v>
+        <v>-0.2758</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8114</v>
+        <v>3.778</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8114</v>
+        <v>3.6689</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.1091</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2456</v>
+        <v>-0.5011</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2351</v>
+        <v>-0.1161</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4807</v>
+        <v>-0.3849</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.0995</v>
+        <v>-0.733</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R15" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8075</v>
+        <v>1.7907</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8484</v>
+        <v>1.7523</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.041</v>
+        <v>0.0384</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0049</v>
+        <v>2.9349</v>
       </c>
       <c r="E16" t="n">
         <v>0.9945000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0104</v>
+        <v>1.9404</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4864</v>
@@ -1702,13 +1702,13 @@
         <v>2.7489</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0044</v>
+        <v>0.9344</v>
       </c>
       <c r="T16" t="n">
         <v>0.6388</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3656</v>
+        <v>0.2956</v>
       </c>
       <c r="V16" t="n">
         <v>0.6543</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.9793</v>
+        <v>2.8112</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1336</v>
+        <v>1.6144</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8456</v>
+        <v>1.1968</v>
       </c>
       <c r="G17" t="n">
         <v>2.8389</v>
@@ -1780,13 +1780,13 @@
         <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3099</v>
+        <v>0.5221</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0355</v>
+        <v>0.5162</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3453</v>
+        <v>0.0058</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7898</v>
+        <v>2.3932</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7366</v>
+        <v>1.7366</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5264</v>
+        <v>0.6567</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7246</v>
+        <v>1.0602</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3787</v>
+        <v>2.1402</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6541</v>
+        <v>-1.08</v>
       </c>
       <c r="J18" t="n">
-        <v>2.105</v>
+        <v>0.7186</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6627</v>
+        <v>1.9908</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5577</v>
+        <v>-1.2722</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3804</v>
+        <v>0.3416</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.284</v>
+        <v>0.1495</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0964</v>
+        <v>0.1922</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7982</v>
+        <v>1.4613</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0927</v>
+        <v>0.9789</v>
       </c>
       <c r="U18" t="n">
-        <v>0.891</v>
+        <v>0.4824</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.3115</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4069</v>
+        <v>1.9951</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7751</v>
+        <v>-0.1597</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6319</v>
+        <v>2.1548</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0602</v>
+        <v>1.7246</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1402</v>
+        <v>2.3787</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.08</v>
+        <v>-0.6541</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7186</v>
+        <v>2.105</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9908</v>
+        <v>2.6627</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2722</v>
+        <v>-0.5577</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3416</v>
+        <v>-0.3804</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1495</v>
+        <v>-0.284</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1922</v>
+        <v>-0.0964</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1833</v>
+        <v>-0.733</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R19" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S19" t="n">
-        <v>0.475</v>
+        <v>1.0036</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0174</v>
+        <v>0.4842</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4577</v>
+        <v>0.5194</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3115</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9529</v>
+        <v>0.9502</v>
       </c>
       <c r="E20" t="n">
-        <v>1.193</v>
+        <v>0.9502</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2401</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5336</v>
+        <v>0.9502</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1264</v>
+        <v>0.3251</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4072</v>
+        <v>0.6251</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6584</v>
+        <v>0.9502</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0591</v>
+        <v>0.3251</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5994</v>
+        <v>0.6251</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1249</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0673</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1922</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7534999999999999</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5845</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.169</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9502</v>
+        <v>0.6163</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9502</v>
+        <v>1.0007</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.3844</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9502</v>
+        <v>-0.5336</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3251</v>
+        <v>-0.1264</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6251</v>
+        <v>-0.4072</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9502</v>
+        <v>-0.6584</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3251</v>
+        <v>-0.0591</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6251</v>
+        <v>-0.5994</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>0.1249</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.0673</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.1922</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.4169</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.3922</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.0247</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8205</v>
+        <v>-0.0177</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4236</v>
+        <v>0.0572</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3969</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>0.4888</v>
@@ -2170,13 +2170,13 @@
         <v>0.9163</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2702</v>
+        <v>-0.4674</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7157</v>
+        <v>-0.2349</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5545</v>
+        <v>-0.2325</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9554</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4903</v>
+        <v>-0.9352</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.435</v>
+        <v>-0.9542</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0553</v>
+        <v>0.019</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4953</v>
@@ -2248,13 +2248,13 @@
         <v>0.3665</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4452</v>
+        <v>0.1099</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3854</v>
+        <v>0.0954</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0598</v>
+        <v>0.0145</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.716</v>
+        <v>-2.6917</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3727</v>
+        <v>-4.6996</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6568</v>
+        <v>2.0079</v>
       </c>
       <c r="G24" t="n">
         <v>-3.8459</v>
@@ -2326,13 +2326,13 @@
         <v>1.8326</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4094</v>
+        <v>-0.3852</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6795</v>
+        <v>-0.0064</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.73</v>
+        <v>-0.3788</v>
       </c>
       <c r="V24" t="n">
         <v>0.6231</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.33</v>
+        <v>14.971</v>
       </c>
       <c r="E25" t="n">
-        <v>6.028399999999998</v>
+        <v>6.028499999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>8.301700000000002</v>
+        <v>8.942599999999999</v>
       </c>
       <c r="G25" t="n">
         <v>9.035399999999997</v>
@@ -2404,13 +2404,13 @@
         <v>13.7442</v>
       </c>
       <c r="S25" t="n">
-        <v>5.313</v>
+        <v>5.954</v>
       </c>
       <c r="T25" t="n">
-        <v>5.0228</v>
+        <v>5.022799999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2902</v>
+        <v>0.9310999999999998</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9344999999999999</v>
